--- a/app/Archivos/Template/Template_HRC_farmatodo.xlsx
+++ b/app/Archivos/Template/Template_HRC_farmatodo.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9/16/25</t>
+          <t>9/18/25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/app/Archivos/Template/Template_HRC_farmatodo.xlsx
+++ b/app/Archivos/Template/Template_HRC_farmatodo.xlsx
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="64" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>218819138.28</v>
+        <v>218819139.43</v>
       </c>
     </row>
     <row r="7">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>218819138.28</v>
+        <v>218819139.43</v>
       </c>
     </row>
     <row r="8">
@@ -781,7 +781,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9/18/25</t>
+          <t>#m/#d/25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>218819138.28</v>
+        <v>218819139.43</v>
       </c>
     </row>
     <row r="13"/>
@@ -838,12 +838,12 @@
     <row r="19">
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Nota Debito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>‭PMP1279547‬</t>
+          <t>PMP1279547</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
@@ -854,21 +854,17 @@
       <c r="H19" s="6" t="n">
         <v>126062332.48</v>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ‭PMP1279547‬</t>
-        </is>
-      </c>
+      <c r="I19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Nota Debito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>‭PMP1279567‬</t>
+          <t>PMP1279567</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
@@ -879,21 +875,17 @@
       <c r="H20" s="6" t="n">
         <v>93147129.05</v>
       </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ‭PMP1279567‬</t>
-        </is>
-      </c>
+      <c r="I20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Nota Debito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>‭PMP1279890‬</t>
+          <t>PMP1279890</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
@@ -904,11 +896,7 @@
       <c r="H21" s="6" t="n">
         <v>3344306.86</v>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ‭PMP1279890‬</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="C22" s="10" t="inlineStr">
@@ -918,20 +906,28 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>‭NC-PMP1279547‬</t>
+          <t>PMP1279547</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
         <v>-2118694.66</v>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>DPP</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="H22" s="6" t="n">
         <v>-2118694.66</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ‭NC-PMP1279547‬</t>
+          <t>DPP PMP1279547 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
         </is>
       </c>
     </row>
@@ -943,20 +939,28 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>‭NC-PMP1279567‬</t>
+          <t>PMP1279567</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
         <v>-1565497.97</v>
       </c>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>DPP</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="H23" s="6" t="n">
         <v>-1565497.97</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ‭NC-PMP1279567‬</t>
+          <t>DPP PMP1279567 OC:14007453 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
         </is>
       </c>
     </row>
@@ -968,72 +972,127 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>‭NC-PMP1279890‬</t>
+          <t>PMP1279890</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
         <v>-50437.48</v>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>DPP</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="H24" s="6" t="n">
         <v>-50437.48</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ‭NC-PMP1279890‬</t>
+          <t>DPP PMP1279890 OC:14007449 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>PMP1279547</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.7000000029802322</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.7000000029802322</v>
+      </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t> </t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>PMP1279567</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.3100000023841858</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.3100000023841858</v>
+      </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t> </t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="10" t="inlineStr"/>
-      <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>PMP1279890</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.1400000001303852</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.1400000001303852</v>
+      </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="10" t="inlineStr"/>
-      <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr"/>
-      <c r="G28" s="10" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr"/>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>

--- a/app/Archivos/Template/Template_HRC_farmatodo.xlsx
+++ b/app/Archivos/Template/Template_HRC_farmatodo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unilever-my.sharepoint.com/personal/jose-ricardo_morales_unilever_com/Documents/Cartera/PROYECTOS/Cash App Cross Andina/Python/Unilever_Collect_Digital/app/Archivos/Template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_C9568FE7F41C531F26EFD9F42AE1C217CA5D1ED4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC6D9F72-E39A-4181-9716-41C6AF5E4F91}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_C9568FE7F49C54DDB674F9B43CE1C217CA5D1EFC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94917A65-20FB-4CD6-AFEB-EEA3F3EB2F26}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Remittance" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>Desglose de Pago</t>
   </si>
@@ -62,12 +75,6 @@
     <t>Valor</t>
   </si>
   <si>
-    <t>9/23/25</t>
-  </si>
-  <si>
-    <t>Transferencia</t>
-  </si>
-  <si>
     <t>Tipo de Documento</t>
   </si>
   <si>
@@ -107,19 +114,25 @@
     <t>NDNC-DC04-757791</t>
   </si>
   <si>
-    <t xml:space="preserve"> NDNC-DC04-757791 Liquidaciones ventas pos Agosto - Cuidado De La Mama</t>
+    <t>NOTAS CREDITO</t>
+  </si>
+  <si>
+    <t>987</t>
+  </si>
+  <si>
+    <t>Saldo FC NDNC-DC04-757791</t>
   </si>
   <si>
     <t>NDNC-DC04-757790</t>
   </si>
   <si>
-    <t xml:space="preserve"> NDNC-DC04-757790 Liquidaciones ventas pos Agosto - Horas De Locura 31 a 1</t>
+    <t>Saldo FC NDNC-DC04-757790</t>
   </si>
   <si>
     <t>NDNC-DC04-757789</t>
   </si>
   <si>
-    <t xml:space="preserve"> NDNC-DC04-757789 Liquidaciones ventas pos Agosto - Semana Lactancia</t>
+    <t>Saldo FC NDNC-DC04-757789</t>
   </si>
   <si>
     <t>Factura</t>
@@ -131,31 +144,31 @@
     <t>Descuentos no asociados a FC</t>
   </si>
   <si>
+    <t>DPP</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>DPP PMP1279546 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+  </si>
+  <si>
     <t>NCNC-DC04-757790</t>
   </si>
   <si>
-    <t xml:space="preserve"> NCNC-DC04-757790 Cobro Descuento Apoyo Apertura mes de Agosto (Cerritos, Americas, Palmas)</t>
+    <t>Myr Vlr Pagado NCNC-DC04-757790</t>
   </si>
   <si>
     <t>NCNC-DC04-757791</t>
   </si>
   <si>
-    <t xml:space="preserve"> NCNC-DC04-757791 Ponds Serum solar</t>
+    <t>Myr Vlr Pagado NCNC-DC04-757791</t>
   </si>
   <si>
     <t>NCNC-DC04-757789</t>
   </si>
   <si>
-    <t xml:space="preserve"> NCNC-DC04-757789 Negociaciones Unilever</t>
-  </si>
-  <si>
-    <t>DPP</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>DPP PMP1279546 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+    <t>Myr Vlr Pagado NCNC-DC04-757789</t>
   </si>
   <si>
     <t>CNQPMP1279546</t>
@@ -296,7 +309,7 @@
     <t>                    </t>
   </si>
   <si>
-    <t>987</t>
+    <t>384</t>
   </si>
 </sst>
 </file>
@@ -491,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -548,6 +561,15 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -558,15 +580,9 @@
     <xf numFmtId="4" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -869,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:I29"/>
+  <dimension ref="C2:I30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
@@ -879,7 +895,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="93" customWidth="1"/>
+    <col min="9" max="9" width="66" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:8" x14ac:dyDescent="0.3">
@@ -909,7 +925,8 @@
         <v>5</v>
       </c>
       <c r="G6" s="4">
-        <v>-4.6899999380111694</v>
+        <f>SUM(H19:H32)</f>
+        <v>4.9415976199895795E-8</v>
       </c>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
@@ -919,7 +936,8 @@
         <v>6</v>
       </c>
       <c r="G7" s="4">
-        <v>-4.6899999468587339</v>
+        <f>SUM(H19:H32)</f>
+        <v>4.9415976199895795E-8</v>
       </c>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
@@ -933,7 +951,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="4">
-        <v>-8.8475644588470459E-9</v>
+        <v>-1.257285475730896E-8</v>
       </c>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.3">
@@ -951,240 +969,241 @@
       </c>
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12">
-        <v>35183</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
+      <c r="F12" s="5"/>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="H18" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="I18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="7" t="s">
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="5">
+        <v>848224589.05999994</v>
+      </c>
+      <c r="F19" s="33"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="5">
+        <v>848224589.05999994</v>
+      </c>
+      <c r="I19" s="10"/>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="D20" s="33" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="9" t="s">
+      <c r="E20" s="5">
+        <v>-829921733</v>
+      </c>
+      <c r="F20" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="G20" s="9"/>
+      <c r="H20" s="5">
+        <v>-829921733</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="5">
-        <v>-829921733</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9" t="s">
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="5">
-        <v>-829921733</v>
-      </c>
-      <c r="I19" s="10" t="s">
+      <c r="D21" s="33" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="9" t="s">
+      <c r="E21" s="5">
+        <v>10000000</v>
+      </c>
+      <c r="F21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="5">
+      <c r="H21" s="5">
         <v>10000000</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="5">
-        <v>10000000</v>
-      </c>
-      <c r="I20" s="10" t="s">
+      <c r="I21" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="9" t="s">
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="5">
+        <v>39000000</v>
+      </c>
+      <c r="F22" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="G22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="5">
         <v>39000000</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="5">
-        <v>39000000</v>
-      </c>
-      <c r="I21" s="10" t="s">
+      <c r="I22" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="9" t="s">
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="5">
+        <v>70000000</v>
+      </c>
+      <c r="F23" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="G23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="5">
         <v>70000000</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="5">
-        <v>70000000</v>
-      </c>
-      <c r="I22" s="10" t="s">
+      <c r="I23" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="9" t="s">
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="5">
-        <v>848224589.05999994</v>
-      </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="5">
-        <v>848224589.05999994</v>
-      </c>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="5">
+        <v>-14255875.449999999</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="5">
+        <v>-14255875.449999999</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="5">
+      <c r="D25" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="5">
         <v>-39000000</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="5">
+      <c r="F25" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="5">
         <v>-39000000</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="9" t="s">
+      <c r="I25" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="D26" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="5">
         <v>-10000000</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="5">
+      <c r="F26" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="5">
         <v>-10000000</v>
       </c>
-      <c r="I25" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="9" t="s">
+      <c r="I26" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="5">
+      <c r="D27" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="5">
         <v>-70000000</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="5">
+      <c r="F27" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="5">
         <v>-70000000</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="5">
-        <v>-14255875.449999999</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="5">
-        <v>-14255875.449999999</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="33" t="s">
         <v>45</v>
       </c>
       <c r="E28" s="5">
         <v>-4046980.56</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="33" t="s">
         <v>46</v>
       </c>
       <c r="G28" s="9" t="s">
@@ -1198,16 +1217,16 @@
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="33" t="s">
         <v>34</v>
       </c>
       <c r="E29" s="5">
         <v>-4.7399998903274536</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="33" t="s">
         <v>49</v>
       </c>
       <c r="G29" s="9" t="s">
@@ -1217,6 +1236,29 @@
         <v>-4.7399998903274536</v>
       </c>
       <c r="I29" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="5">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="5">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1278,31 +1320,31 @@
       <c r="E6" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="32"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28"/>
     </row>
     <row r="7" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="29">
         <v>35183</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="32">
         <v>829921733.04999995</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="29" t="s">
         <v>61</v>
       </c>
       <c r="F7" s="22" t="s">
@@ -1337,11 +1379,11 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
@@ -1356,11 +1398,11 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
       <c r="F9" s="15" t="s">
         <v>73</v>
       </c>
@@ -1393,11 +1435,11 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
       <c r="F10" s="15" t="s">
         <v>75</v>
       </c>
@@ -1430,11 +1472,11 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="15" t="s">
         <v>77</v>
       </c>
@@ -1467,11 +1509,11 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="15" t="s">
         <v>79</v>
       </c>
@@ -1504,11 +1546,11 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="15" t="s">
         <v>81</v>
       </c>
@@ -1541,11 +1583,11 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="15" t="s">
         <v>83</v>
       </c>
@@ -1578,11 +1620,11 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="15" t="s">
         <v>85</v>
       </c>
@@ -1615,11 +1657,11 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="15" t="s">
         <v>87</v>
       </c>
@@ -1689,23 +1731,23 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/app/Archivos/Template/Template_HRC_farmatodo.xlsx
+++ b/app/Archivos/Template/Template_HRC_farmatodo.xlsx
@@ -673,7 +673,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="66" customWidth="1" min="9" max="9"/>
+    <col width="93" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -717,9 +717,7 @@
           <t>TOTAL s/ BANCOS</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>-4.689999938011169</v>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="C7" s="2" t="n"/>
@@ -730,7 +728,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-4.689999950584024</v>
+        <v>-4.68999994918704</v>
       </c>
     </row>
     <row r="8">
@@ -748,7 +746,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-1.257285475730896e-08</v>
+        <v>-4.68999994918704</v>
       </c>
     </row>
     <row r="9"/>
@@ -779,19 +777,13 @@
       <c r="C12" t="n">
         <v>35183</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>9/24/25</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>-4.689999938011169</v>
-      </c>
+      <c r="F12" s="6" t="inlineStr"/>
     </row>
     <row r="13"/>
     <row r="14"/>
@@ -838,29 +830,25 @@
     <row r="19">
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota Debito</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>1200013673</t>
+          <t>NDNC-DC04-757789</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-829921733</v>
+        <v>70000000</v>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>NRO</t>
-        </is>
-      </c>
+      <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="6" t="n">
-        <v>-829921733</v>
+        <v>70000000</v>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>favor del cliente sin aplicar por falta de soporte</t>
+          <t xml:space="preserve"> NDNC-DC04-757789 Liquidaciones ventas pos Agosto - Semana Lactancia</t>
         </is>
       </c>
     </row>
@@ -872,28 +860,20 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>NDNC-DC04-757791</t>
+          <t>NDNC-DC04-757790</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>NOTAS CREDITO</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>39000000</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="6" t="n">
-        <v>10000000</v>
+        <v>39000000</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC NDNC-DC04-757791</t>
+          <t xml:space="preserve"> NDNC-DC04-757790 Liquidaciones ventas pos Agosto - Horas De Locura 31 a 1</t>
         </is>
       </c>
     </row>
@@ -905,84 +885,72 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>NDNC-DC04-757790</t>
+          <t>NDNC-DC04-757791</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>NOTAS CREDITO</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="6" t="n">
-        <v>39000000</v>
+        <v>10000000</v>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC NDNC-DC04-757790</t>
+          <t xml:space="preserve"> NDNC-DC04-757791 Liquidaciones ventas pos Agosto - Cuidado De La Mama</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Nota Debito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>NDNC-DC04-757789</t>
+          <t>PMP1279546</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>NOTAS CREDITO</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>848224589.0599999</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr"/>
+      <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="6" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>Saldo FC NDNC-DC04-757789</t>
-        </is>
-      </c>
+        <v>848224589.0599999</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>PMP1279546</t>
+          <t>1200013673</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>848224589.0599999</v>
+        <v>-829921733</v>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>NRO</t>
+        </is>
+      </c>
       <c r="H23" s="6" t="n">
-        <v>848224589.0599999</v>
-      </c>
-      <c r="I23" s="11" t="inlineStr"/>
+        <v>-829921733</v>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>favor del cliente sin aplicar por falta de soporte</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="C24" s="10" t="inlineStr">
@@ -992,28 +960,28 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>PMP1279546</t>
+          <t>CNQPMP1279546</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-14255875.45</v>
+        <v>-4046980.56</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>DPP</t>
+          <t>RECHAZOS</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-14255875.45</v>
+        <v>-4046980.56</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>DPP PMP1279546 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+          <t>RECHAZOS CNQPMP1279546 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA</t>
         </is>
       </c>
     </row>
@@ -1025,28 +993,20 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>NCNC-DC04-757790</t>
+          <t>NCNC-DC04-757789</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-39000000</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>NOTAS CREDITO</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>-70000000</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="6" t="n">
-        <v>-39000000</v>
+        <v>-70000000</v>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado NCNC-DC04-757790</t>
+          <t xml:space="preserve"> NCNC-DC04-757789 Negociaciones Unilever</t>
         </is>
       </c>
     </row>
@@ -1058,28 +1018,20 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>NCNC-DC04-757791</t>
+          <t>NCNC-DC04-757790</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>NOTAS CREDITO</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>-39000000</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="6" t="n">
-        <v>-10000000</v>
+        <v>-39000000</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado NCNC-DC04-757791</t>
+          <t xml:space="preserve"> NCNC-DC04-757790 Cobro Descuento Apoyo Apertura mes de Agosto (Cerritos, Americas, Palmas)</t>
         </is>
       </c>
     </row>
@@ -1091,28 +1043,20 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>NCNC-DC04-757789</t>
+          <t>NCNC-DC04-757791</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-70000000</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>NOTAS CREDITO</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>-10000000</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
       <c r="H27" s="6" t="n">
-        <v>-70000000</v>
+        <v>-10000000</v>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado NCNC-DC04-757789</t>
+          <t xml:space="preserve"> NCNC-DC04-757791 Ponds Serum solar</t>
         </is>
       </c>
     </row>
@@ -1124,28 +1068,28 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>CNQPMP1279546</t>
+          <t>PMP1279546</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>-4046980.56</v>
+        <v>-14255875.45</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>RECHAZOS</t>
+          <t>DPP</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-4046980.56</v>
+        <v>-14255875.45</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>RECHAZOS CNQPMP1279546 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA</t>
+          <t>DPP PMP1279546 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
         </is>
       </c>
     </row>

--- a/app/Archivos/Template/Template_HRC_farmatodo.xlsx
+++ b/app/Archivos/Template/Template_HRC_farmatodo.xlsx
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -672,8 +672,8 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="93" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="68" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>35183</v>
+        <v>35264</v>
       </c>
     </row>
     <row r="3"/>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-4.68999994918704</v>
+        <v>38708040.07</v>
       </c>
     </row>
     <row r="8">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-4.68999994918704</v>
+        <v>38708040.07</v>
       </c>
     </row>
     <row r="9"/>
@@ -775,7 +775,7 @@
     </row>
     <row r="12">
       <c r="C12" t="n">
-        <v>35183</v>
+        <v>35264</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
@@ -830,125 +830,141 @@
     <row r="19">
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Nota Debito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>NDNC-DC04-757789</t>
+          <t>PMP1281720</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>70000000</v>
+        <v>14028445.95</v>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="6" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> NDNC-DC04-757789 Liquidaciones ventas pos Agosto - Semana Lactancia</t>
-        </is>
-      </c>
+        <v>14028445.95</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Nota Debito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>NDNC-DC04-757790</t>
+          <t>PMP1281721</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>39000000</v>
+        <v>26826057.33</v>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="6" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> NDNC-DC04-757790 Liquidaciones ventas pos Agosto - Horas De Locura 31 a 1</t>
-        </is>
-      </c>
+        <v>26826057.33</v>
+      </c>
+      <c r="I20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Nota Debito</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>NDNC-DC04-757791</t>
+          <t>PMP1281720</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
+        <v>-235772.2</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>DPP</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="H21" s="6" t="n">
-        <v>10000000</v>
+        <v>-235772.2</v>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NDNC-DC04-757791 Liquidaciones ventas pos Agosto - Cuidado De La Mama</t>
+          <t>DPP PMP1281720 OC:14007843 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>PMP1279546</t>
+          <t>PMP1281721</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>848224589.0599999</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
+        <v>-450858.11</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>DPP</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="H22" s="6" t="n">
-        <v>848224589.0599999</v>
-      </c>
-      <c r="I22" s="11" t="inlineStr"/>
+        <v>-450858.11</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>DPP PMP1281721 OC:14007843 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>1200013673</t>
+          <t>NC100331707</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>-829921733</v>
-      </c>
-      <c r="F23" s="10" t="inlineStr"/>
+        <v>-1459833.98</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>DSCT AVERIAS</t>
+        </is>
+      </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-829921733</v>
+        <v>-1459833.98</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>favor del cliente sin aplicar por falta de soporte</t>
+          <t>DSCT AVERIAS NC100331707 NOTAS DE CREDITO POR DEVOLUCION 100331707</t>
         </is>
       </c>
     </row>
@@ -960,28 +976,28 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>CNQPMP1279546</t>
+          <t>PMP1281720</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-4046980.56</v>
+        <v>0.08999999985098839</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>RECHAZOS</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-4046980.56</v>
+        <v>0.08999999985098839</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>RECHAZOS CNQPMP1279546 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -993,134 +1009,26 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>NCNC-DC04-757789</t>
+          <t>PMP1281721</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-70000000</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
+        <v>0.9900000020861626</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
       <c r="H25" s="6" t="n">
-        <v>-70000000</v>
+        <v>0.9900000020861626</v>
       </c>
       <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> NCNC-DC04-757789 Negociaciones Unilever</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>NCNC-DC04-757790</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>-39000000</v>
-      </c>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="6" t="n">
-        <v>-39000000</v>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> NCNC-DC04-757790 Cobro Descuento Apoyo Apertura mes de Agosto (Cerritos, Americas, Palmas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>NCNC-DC04-757791</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="6" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> NCNC-DC04-757791 Ponds Serum solar</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>PMP1279546</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>-14255875.45</v>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>DPP</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>-14255875.45</v>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>DPP PMP1279546 OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>PMP1279546</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>-4.739999890327454</v>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>WOB</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>-4.739999890327454</v>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
@@ -1137,24 +1045,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.77734375" customWidth="1" min="1" max="1"/>
-    <col width="10.21875" customWidth="1" min="2" max="2"/>
-    <col width="13.6640625" customWidth="1" min="3" max="3"/>
-    <col width="15.6640625" customWidth="1" min="4" max="4"/>
-    <col width="14.5546875" customWidth="1" min="5" max="5"/>
-    <col width="21.77734375" customWidth="1" min="6" max="6"/>
-    <col width="15.109375" customWidth="1" min="7" max="7"/>
-    <col width="37.21875" customWidth="1" min="8" max="8"/>
-    <col width="24.21875" customWidth="1" min="9" max="9"/>
-    <col width="16.77734375" customWidth="1" min="10" max="10"/>
-    <col width="15.6640625" customWidth="1" min="11" max="11"/>
-    <col width="22.6640625" customWidth="1" min="12" max="12"/>
-    <col width="28.33203125" customWidth="1" min="13" max="13"/>
-    <col width="15.6640625" customWidth="1" min="14" max="14"/>
-    <col width="17.5546875" customWidth="1" min="15" max="15"/>
+    <col width="13.21875" customWidth="1" min="1" max="1"/>
+    <col width="10.5546875" customWidth="1" min="2" max="2"/>
+    <col width="14.109375" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18.33203125" customWidth="1" min="6" max="6"/>
+    <col width="15.5546875" customWidth="1" min="7" max="7"/>
+    <col width="38.44140625" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="14.88671875" customWidth="1" min="10" max="10"/>
+    <col width="16.21875" customWidth="1" min="11" max="11"/>
+    <col width="23.44140625" customWidth="1" min="12" max="12"/>
+    <col width="29.21875" customWidth="1" min="13" max="13"/>
+    <col width="16.21875" customWidth="1" min="14" max="14"/>
+    <col width="16.6640625" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" customHeight="1">
@@ -1224,15 +1131,15 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>35183</v>
+        <v>35264</v>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>‭19-SEP-2025‬</t>
+          <t>‭24-SEP-2025‬</t>
         </is>
       </c>
       <c r="D7" s="21" t="n">
-        <v>829921733.05</v>
+        <v>38708038.99</v>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
@@ -1319,22 +1226,22 @@
       <c r="E9" s="23" t="n"/>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>‭NCNC-DC04-757790‬</t>
+          <t>‭NC100331707‬</t>
         </is>
       </c>
       <c r="G9" s="26" t="n">
-        <v>45903</v>
+        <v>45922</v>
       </c>
       <c r="H9" s="27" t="inlineStr">
         <is>
-          <t>Cobro Descuento Apoyo Apertura mes de Agosto (Cerritos, Americas, Palmas)</t>
+          <t>NOTAS DE CREDITO POR DEVOLUCION 100331707</t>
         </is>
       </c>
       <c r="I9" s="28" t="n">
-        <v>-39000000</v>
-      </c>
-      <c r="J9" s="29" t="n">
-        <v>0</v>
+        <v>-1226751.24</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>-233082.74</v>
       </c>
       <c r="K9" s="29" t="n">
         <v>0</v>
@@ -1349,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>-39000000</v>
+        <v>-1459833.98</v>
       </c>
     </row>
     <row r="10" ht="15.6" customHeight="1">
@@ -1360,22 +1267,22 @@
       <c r="E10" s="23" t="n"/>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>‭NDNC-DC04-757791‬</t>
+          <t>‭PMP1281720‬</t>
         </is>
       </c>
       <c r="G10" s="26" t="n">
-        <v>45903</v>
+        <v>45899</v>
       </c>
       <c r="H10" s="27" t="inlineStr">
         <is>
-          <t>Liquidaciones ventas pos Agosto - Cuidado De La Mama</t>
+          <t>OC:14007843 UNILEVER ANDINA COLOMBIA LTDA</t>
         </is>
       </c>
       <c r="I10" s="28" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>0</v>
+        <v>11788610.04</v>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>2239835.91</v>
       </c>
       <c r="K10" s="29" t="n">
         <v>0</v>
@@ -1390,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>10000000</v>
+        <v>14028445.95</v>
       </c>
     </row>
     <row r="11" ht="15.6" customHeight="1">
@@ -1401,19 +1308,19 @@
       <c r="E11" s="23" t="n"/>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>‭NDNC-DC04-757790‬</t>
+          <t>‭NC-PMP1281721‬</t>
         </is>
       </c>
       <c r="G11" s="26" t="n">
-        <v>45903</v>
+        <v>45899</v>
       </c>
       <c r="H11" s="27" t="inlineStr">
         <is>
-          <t>Liquidaciones ventas pos Agosto - Horas De Locura 31 a 1</t>
-        </is>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>39000000</v>
+          <t>OC:14007843 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="29" t="n">
         <v>0</v>
@@ -1424,14 +1331,14 @@
       <c r="L11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="29" t="n">
-        <v>0</v>
+      <c r="M11" s="28" t="n">
+        <v>-450858.11</v>
       </c>
       <c r="N11" s="29" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>39000000</v>
+        <v>-450858.11</v>
       </c>
     </row>
     <row r="12" ht="15.6" customHeight="1">
@@ -1442,19 +1349,19 @@
       <c r="E12" s="23" t="n"/>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>‭NDNC-DC04-757789‬</t>
+          <t>‭NC-PMP1281720‬</t>
         </is>
       </c>
       <c r="G12" s="26" t="n">
-        <v>45903</v>
+        <v>45899</v>
       </c>
       <c r="H12" s="27" t="inlineStr">
         <is>
-          <t>Liquidaciones ventas pos Agosto - Semana Lactancia</t>
-        </is>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>70000000</v>
+          <t>OC:14007843 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+        </is>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="29" t="n">
         <v>0</v>
@@ -1465,40 +1372,40 @@
       <c r="L12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="29" t="n">
-        <v>0</v>
+      <c r="M12" s="28" t="n">
+        <v>-235772.2</v>
       </c>
       <c r="N12" s="29" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>70000000</v>
+        <v>-235772.2</v>
       </c>
     </row>
     <row r="13" ht="15.6" customHeight="1">
-      <c r="A13" s="23" t="n"/>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>‭NCNC-DC04-757791‬</t>
+          <t>‭PMP1281721‬</t>
         </is>
       </c>
       <c r="G13" s="26" t="n">
-        <v>45903</v>
+        <v>45899</v>
       </c>
       <c r="H13" s="27" t="inlineStr">
         <is>
-          <t>Ponds Serum solar</t>
+          <t>OC:14007843 UNILEVER ANDINA COLOMBIA LTDA</t>
         </is>
       </c>
       <c r="I13" s="28" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
+        <v>22542905.32</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>4283152.01</v>
       </c>
       <c r="K13" s="29" t="n">
         <v>0</v>
@@ -1513,178 +1420,14 @@
         <v>0</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>-10000000</v>
-      </c>
-    </row>
-    <row r="14" ht="15.6" customHeight="1">
-      <c r="A14" s="23" t="n"/>
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>‭NCNC-DC04-757789‬</t>
-        </is>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>45903</v>
-      </c>
-      <c r="H14" s="27" t="inlineStr">
-        <is>
-          <t>Negociaciones Unilever</t>
-        </is>
-      </c>
-      <c r="I14" s="28" t="n">
-        <v>-70000000</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="28" t="n">
-        <v>-70000000</v>
-      </c>
-    </row>
-    <row r="15" ht="15.6" customHeight="1">
-      <c r="A15" s="23" t="n"/>
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>‭CNQPMP1279546‬</t>
-        </is>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>45918</v>
-      </c>
-      <c r="H15" s="27" t="inlineStr">
-        <is>
-          <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA</t>
-        </is>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>-3400824</v>
-      </c>
-      <c r="J15" s="28" t="n">
-        <v>-646156.5600000001</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>-4046980.56</v>
-      </c>
-    </row>
-    <row r="16" ht="15.6" customHeight="1">
-      <c r="A16" s="23" t="n"/>
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>‭PMP1279546‬</t>
-        </is>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>45895</v>
-      </c>
-      <c r="H16" s="27" t="inlineStr">
-        <is>
-          <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA</t>
-        </is>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>712793772.3200001</v>
-      </c>
-      <c r="J16" s="28" t="n">
-        <v>135430816.74</v>
-      </c>
-      <c r="K16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>848224589.0599999</v>
-      </c>
-    </row>
+        <v>26826057.33</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" ht="15.6" customHeight="1">
-      <c r="A17" s="24" t="n"/>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>‭NC-PMP1279546‬</t>
-        </is>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>45895</v>
-      </c>
-      <c r="H17" s="27" t="inlineStr">
-        <is>
-          <t>OC:14007431 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
-        </is>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="28" t="n">
-        <v>-14255875.45</v>
-      </c>
-      <c r="N17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="28" t="n">
-        <v>-14255875.45</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21" ht="15.6" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>                     </t>
         </is>
@@ -1693,20 +1436,20 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="M7:M8"/>
-    <mergeCell ref="C7:C17"/>
-    <mergeCell ref="A7:A17"/>
-    <mergeCell ref="B7:B17"/>
-    <mergeCell ref="E7:E17"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="E7:E13"/>
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="I7:I8"/>
-    <mergeCell ref="D7:D17"/>
+    <mergeCell ref="A17:O17"/>
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="J7:J8"/>
-    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="D7:D13"/>
     <mergeCell ref="F6:O6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
